--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104510_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104510_W6.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7993</v>
+        <v>7.96</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3545</v>
+        <v>5.6607</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4447</v>
+        <v>2.2993</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0029</v>
+        <v>7.0146</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0952</v>
+        <v>3.0933</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9078</v>
+        <v>3.9213</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8182</v>
+        <v>5.7869</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0118</v>
+        <v>1.9887</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8063</v>
+        <v>3.7982</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1848</v>
+        <v>1.2277</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0833</v>
+        <v>1.1046</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1015</v>
+        <v>0.1231</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2322</v>
+        <v>-1.0726</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9043</v>
+        <v>-0.5508</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3279</v>
+        <v>-0.5218</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5748</v>
+        <v>1.5628</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5748</v>
+        <v>1.5628</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8078</v>
+        <v>3.8179</v>
       </c>
       <c r="E3" t="n">
-        <v>1.931</v>
+        <v>2.1206</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8768</v>
+        <v>1.6973</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3644</v>
+        <v>5.3686</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5584</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>4.806</v>
+        <v>4.8086</v>
       </c>
       <c r="J3" t="n">
-        <v>5.006</v>
+        <v>4.9754</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4187</v>
+        <v>0.403</v>
       </c>
       <c r="L3" t="n">
-        <v>4.5873</v>
+        <v>4.5725</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3584</v>
+        <v>0.3931</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1397</v>
+        <v>0.157</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2187</v>
+        <v>0.2361</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8326</v>
+        <v>-0.8207</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7652</v>
+        <v>-0.5298</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0675</v>
+        <v>-0.2909</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3176</v>
+        <v>1.3187</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Z. HANKINS</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4753</v>
+        <v>1.4339</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7419</v>
+        <v>1.3415</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2666</v>
+        <v>0.0924</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0639</v>
+        <v>1.4564</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5223</v>
+        <v>2.5273</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4584</v>
+        <v>-1.0709</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5866</v>
+        <v>1.7807</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4373</v>
+        <v>1.9822</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1493</v>
+        <v>-0.2015</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4773</v>
+        <v>-0.3243</v>
       </c>
       <c r="N4" t="n">
-        <v>1.085</v>
+        <v>0.5451</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6077</v>
+        <v>-0.8694</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S4" t="n">
-        <v>1.077</v>
+        <v>-1.2517</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1553</v>
+        <v>-0.4392</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0784</v>
+        <v>-0.8126</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.3461</v>
+        <v>0.7739</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.3461</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1783</v>
+        <v>1.1471</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3989</v>
+        <v>0.5124</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7794</v>
+        <v>0.6347</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3905</v>
+        <v>0.3952</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7849</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3945</v>
+        <v>-0.3916</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8858</v>
+        <v>0.8818</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4954</v>
+        <v>-0.4866</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2102</v>
+        <v>-0.2497</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2767</v>
+        <v>0.1198</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>Z. HANKINS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0614</v>
+        <v>0.6381</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2429</v>
+        <v>1.9115</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1815</v>
+        <v>-1.2734</v>
       </c>
       <c r="G6" t="n">
-        <v>1.451</v>
+        <v>2.0722</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5251</v>
+        <v>2.5217</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0742</v>
+        <v>-0.4495</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7994</v>
+        <v>1.5796</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9914</v>
+        <v>1.4307</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.192</v>
+        <v>0.1489</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3485</v>
+        <v>0.4926</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5337</v>
+        <v>1.0911</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8822</v>
+        <v>-0.5984</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6145</v>
+        <v>0.2197</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5565</v>
+        <v>0.3319</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.058</v>
+        <v>-0.1122</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7712</v>
+        <v>-2.3367</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7712</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3444</v>
+        <v>0.5702</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.279</v>
+        <v>-0.5566</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6234</v>
+        <v>1.1268</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5133</v>
+        <v>1.5096</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0317</v>
+        <v>-2.0279</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5451</v>
+        <v>3.5375</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1818</v>
+        <v>1.1441</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.9896</v>
+        <v>-3.0034</v>
       </c>
       <c r="L7" t="n">
-        <v>4.1714</v>
+        <v>4.1475</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3316</v>
+        <v>0.3655</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9578</v>
+        <v>0.9755</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6263</v>
+        <v>-0.61</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3958</v>
+        <v>-1.167</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3266</v>
+        <v>-0.5625</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0692</v>
+        <v>-0.6045</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,22 +1033,22 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1060,13 +1060,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0348</v>
+        <v>-0.8797</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0256</v>
+        <v>-0.0359</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0092</v>
+        <v>-0.8438</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5861</v>
+        <v>-0.5833</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1516</v>
+        <v>-0.1467</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4345</v>
+        <v>-0.4365</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4397</v>
+        <v>0.4336</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3705</v>
+        <v>0.3647</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0258</v>
+        <v>-1.0169</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8363</v>
+        <v>-0.6818</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6261</v>
+        <v>-0.6273</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2102</v>
+        <v>-0.0545</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>L. COSTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8837</v>
+        <v>-1.5663</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5572</v>
+        <v>-4.1105</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3265</v>
+        <v>2.5442</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0695</v>
+        <v>1.8531</v>
       </c>
       <c r="H10" t="n">
-        <v>0.427</v>
+        <v>-0.6983</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6425</v>
+        <v>2.5514</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5292</v>
+        <v>1.1601</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6336000000000001</v>
+        <v>-1.2001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8956</v>
+        <v>2.3602</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4597</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2066</v>
+        <v>0.5018</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2531</v>
+        <v>0.1912</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-4.325</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-5.6908</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9285</v>
+        <v>-0.8</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.113</v>
+        <v>-0.6692</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1845</v>
+        <v>-0.1308</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0246</v>
+        <v>1.7057</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. COSTA</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0047</v>
+        <v>-2.1762</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.294</v>
+        <v>-0.5782</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2893</v>
+        <v>-1.598</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8531</v>
+        <v>1.0921</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7057</v>
+        <v>0.4361</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5588</v>
+        <v>0.656</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1884</v>
+        <v>1.5175</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1917</v>
+        <v>0.6238</v>
       </c>
       <c r="L11" t="n">
-        <v>2.3802</v>
+        <v>0.8937</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6647</v>
+        <v>-0.4254</v>
       </c>
       <c r="N11" t="n">
-        <v>0.486</v>
+        <v>-0.1877</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1787</v>
+        <v>-0.2377</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.3098</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.6708</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2512</v>
+        <v>-1.2471</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9043</v>
+        <v>-1.1152</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3469</v>
+        <v>-0.1319</v>
       </c>
       <c r="V11" t="n">
-        <v>1.7032</v>
+        <v>-2.0212</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6105</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8345</v>
+        <v>-4.0331</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.521</v>
+        <v>-3.5614</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3135</v>
+        <v>-0.4717</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2482</v>
+        <v>-0.2406</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7056</v>
+        <v>1.706</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9538</v>
+        <v>-1.9466</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1984</v>
+        <v>-0.2177</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1878</v>
+        <v>1.1754</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0498</v>
+        <v>-0.0229</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0023</v>
+        <v>-1.1959</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7652</v>
+        <v>-0.7667</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2371</v>
+        <v>-0.4292</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9961</v>
+        <v>-1.0032</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2891</v>
+        <v>-0.3007</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.0661</v>
+        <v>7.069799999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9924</v>
+        <v>2.7041</v>
       </c>
       <c r="F13" t="n">
-        <v>4.0736</v>
+        <v>4.365699999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>20.0316</v>
+        <v>20.0958</v>
       </c>
       <c r="H13" t="n">
-        <v>8.7295</v>
+        <v>8.7583</v>
       </c>
       <c r="I13" t="n">
-        <v>11.3021</v>
+        <v>11.3376</v>
       </c>
       <c r="J13" t="n">
-        <v>19.2367</v>
+        <v>19.042</v>
       </c>
       <c r="K13" t="n">
-        <v>4.417100000000001</v>
+        <v>4.313800000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>14.8198</v>
+        <v>14.7283</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7949000000000002</v>
+        <v>1.0537</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3122</v>
+        <v>4.444500000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.5175</v>
+        <v>-3.3908</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7442</v>
+        <v>-14.7962</v>
       </c>
       <c r="R13" t="n">
-        <v>9.073300000000001</v>
+        <v>9.1053</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.226599999999999</v>
+        <v>-8.2668</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.2928</v>
+        <v>-5.2983</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.934</v>
+        <v>-2.968599999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9319000000000006</v>
+        <v>0.9316999999999993</v>
       </c>
       <c r="W13" t="n">
-        <v>3.7925</v>
+        <v>3.756699999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.8607</v>
+        <v>-2.8249</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8249</v>
+        <v>4.7112</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7836</v>
+        <v>5.2949</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9587</v>
+        <v>-0.5838</v>
       </c>
       <c r="G14" t="n">
-        <v>1.243</v>
+        <v>1.254</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.423</v>
+        <v>-0.4113</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6659</v>
+        <v>1.6654</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7741</v>
+        <v>3.7601</v>
       </c>
       <c r="K14" t="n">
-        <v>0.381</v>
+        <v>0.3792</v>
       </c>
       <c r="L14" t="n">
-        <v>3.3931</v>
+        <v>3.3809</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.5311</v>
+        <v>-2.5061</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5139</v>
+        <v>0.3888</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7561</v>
+        <v>0.2876</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2423</v>
+        <v>0.1013</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3637</v>
+        <v>4.1675</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8041</v>
+        <v>5.4241</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4404</v>
+        <v>-1.2566</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4802</v>
+        <v>-0.4828</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.251</v>
+        <v>-0.2581</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2292</v>
+        <v>-0.2247</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1787</v>
+        <v>3.1564</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6785</v>
+        <v>0.6615</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5002</v>
+        <v>2.4949</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.6588</v>
+        <v>-3.6392</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.7294</v>
+        <v>-2.7196</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4582</v>
+        <v>0.2633</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8257</v>
+        <v>0.4757</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3675</v>
+        <v>-0.2124</v>
       </c>
       <c r="V15" t="n">
-        <v>2.571</v>
+        <v>2.5659</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8215</v>
+        <v>2.2868</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6704</v>
+        <v>1.7732</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1511</v>
+        <v>0.5135</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3107</v>
+        <v>1.3101</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6248</v>
+        <v>2.6223</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3141</v>
+        <v>-1.3123</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1392</v>
+        <v>2.1242</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2165</v>
+        <v>2.2063</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8285</v>
+        <v>-0.8141</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4082</v>
+        <v>0.416</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3965</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4688</v>
+        <v>-0.351</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0723</v>
+        <v>0.4171</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4896</v>
+        <v>1.1907</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0416</v>
+        <v>1.7117</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.552</v>
+        <v>-0.521</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6423</v>
+        <v>0.6322</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7993</v>
+        <v>-1.8062</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4416</v>
+        <v>2.4384</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1367</v>
+        <v>2.1081</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6967</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>2.8334</v>
+        <v>2.8223</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4944</v>
+        <v>-1.4759</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0847</v>
+        <v>0.6268</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4657</v>
+        <v>0.2457</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3811</v>
+        <v>0.3812</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W17" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4061</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2223</v>
+        <v>0.9382</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1838</v>
+        <v>-0.8401</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5926</v>
+        <v>-2.1663</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0058</v>
+        <v>-2.6736</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4132</v>
+        <v>0.5073</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0227</v>
+        <v>0.4556</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.769</v>
+        <v>-1.7107</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7463</v>
+        <v>2.1663</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5699</v>
+        <v>-2.6219</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2368</v>
+        <v>-0.9629</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3331</v>
+        <v>-1.659</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9553</v>
+        <v>0.671</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0162</v>
+        <v>0.4826</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9391</v>
+        <v>0.1884</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8639</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.2061</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9779</v>
+        <v>-0.2537</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0566</v>
+        <v>0.0476</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1456</v>
+        <v>-0.5853</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6679</v>
+        <v>-1.0025</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5223</v>
+        <v>0.4173</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>-0.0277</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6908</v>
+        <v>-0.7724</v>
       </c>
       <c r="L19" t="n">
-        <v>2.1909</v>
+        <v>0.7447</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6457</v>
+        <v>-0.5576</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9771</v>
+        <v>-0.2301</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6685</v>
+        <v>-0.3275</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4791</v>
+        <v>1.332</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4779</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0012</v>
+        <v>0.7842</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.8634</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>Y. SIMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8519</v>
+        <v>-0.9418</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9184</v>
+        <v>-1.7823</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0664</v>
+        <v>0.8405</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4135</v>
+        <v>-1.2799</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4329</v>
+        <v>-1.2234</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9806</v>
+        <v>-0.0565</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6118</v>
+        <v>-1.5103</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1803</v>
+        <v>-1.5103</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4316</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8017</v>
+        <v>0.2305</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2526</v>
+        <v>0.287</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.549</v>
+        <v>-0.0565</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2025</v>
+        <v>0.2682</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5989</v>
+        <v>-0.272</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6037</v>
+        <v>0.5402</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3214</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.4498</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Y. SIMA</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2063</v>
+        <v>-1.2762</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1295</v>
+        <v>-3.1852</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9232</v>
+        <v>1.909</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2793</v>
+        <v>-2.4262</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2207</v>
+        <v>-0.4309</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0586</v>
+        <v>-1.9952</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5034</v>
+        <v>-1.6397</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5034</v>
+        <v>-0.1864</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.4533</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2241</v>
+        <v>-0.7865</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2828</v>
+        <v>-0.2446</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0586</v>
+        <v>-0.5419</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>0.007</v>
+        <v>0.7826</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6261</v>
+        <v>0.3665</v>
       </c>
       <c r="U21" t="n">
-        <v>0.633</v>
+        <v>0.416</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1607</v>
+        <v>-0.3155</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0439</v>
+        <v>-2.7887</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2012</v>
+        <v>-1.0343</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8427</v>
+        <v>-1.7544</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9691</v>
+        <v>-0.9961</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0403</v>
+        <v>1.8532</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0095</v>
+        <v>-2.8493</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8847</v>
+        <v>1.8679</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1039</v>
+        <v>2.4714</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9886</v>
+        <v>-0.6035</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0844</v>
+        <v>-2.864</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0636</v>
+        <v>-0.6182</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0209</v>
+        <v>-2.2458</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>2.1087</v>
+        <v>1.209</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4548</v>
+        <v>-0.0097</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6539</v>
+        <v>1.2187</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7712</v>
+        <v>-0.6162</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8835</v>
+        <v>-3.0471</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9376</v>
+        <v>-2.1595</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9459</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9913999999999999</v>
+        <v>-2.9743</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8659</v>
+        <v>0.0457</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.8574</v>
+        <v>-3.0199</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8969</v>
+        <v>-1.9008</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4967</v>
+        <v>0.1034</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5998</v>
+        <v>-2.0042</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8884</v>
+        <v>-1.0734</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6308</v>
+        <v>-0.0578</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.2576</v>
+        <v>-1.0157</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>1.106</v>
+        <v>1.1077</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9557</v>
+        <v>0.5152</v>
       </c>
       <c r="U23" t="n">
-        <v>2.0617</v>
+        <v>0.5925</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6105</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2534</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.924</v>
+        <v>-5.0186</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6473</v>
+        <v>-3.7802</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2768</v>
+        <v>-1.2384</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.6153</v>
+        <v>-4.6224</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.5308</v>
+        <v>-2.5385</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0844</v>
+        <v>-2.084</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.0908</v>
+        <v>-3.1041</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.3418</v>
+        <v>-2.3517</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5245</v>
+        <v>-1.5184</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3354</v>
+        <v>-1.3315</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5985</v>
+        <v>0.5144</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5777</v>
+        <v>0.4621</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9836</v>
+        <v>-6.2455</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.7397</v>
+        <v>-7.3125</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7561</v>
+        <v>1.0669</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.7405</v>
+        <v>-7.7589</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.9291</v>
+        <v>-2.9349</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.8114</v>
+        <v>-4.8239</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.307</v>
+        <v>-6.3435</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.0069</v>
+        <v>-3.0207</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.3001</v>
+        <v>-3.3229</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4335</v>
+        <v>-1.4154</v>
       </c>
       <c r="N25" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2786</v>
+        <v>1.0369</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2571</v>
+        <v>0.2179</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5356</v>
+        <v>0.819</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.0661</v>
+        <v>-7.0697</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.073800000000002</v>
+        <v>-4.3656</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.9925</v>
+        <v>-2.7044</v>
       </c>
       <c r="G26" t="n">
-        <v>-20.0315</v>
+        <v>-20.0959</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.7295</v>
+        <v>-8.758199999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-11.3022</v>
+        <v>-11.3374</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7948000000000004</v>
+        <v>-1.053799999999997</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.3123</v>
+        <v>-4.4446</v>
       </c>
       <c r="L26" t="n">
-        <v>3.5175</v>
+        <v>3.390699999999998</v>
       </c>
       <c r="M26" t="n">
-        <v>-19.2368</v>
+        <v>-19.042</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.4171</v>
+        <v>-4.3139</v>
       </c>
       <c r="O26" t="n">
-        <v>-14.8196</v>
+        <v>-14.7282</v>
       </c>
       <c r="P26" t="n">
-        <v>5.6707</v>
+        <v>5.690699999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-9.0733</v>
+        <v>-9.1053</v>
       </c>
       <c r="R26" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S26" t="n">
-        <v>8.226600000000001</v>
+        <v>8.266899999999998</v>
       </c>
       <c r="T26" t="n">
-        <v>2.9339</v>
+        <v>2.9685</v>
       </c>
       <c r="U26" t="n">
-        <v>5.2927</v>
+        <v>5.2985</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.9317999999999999</v>
+        <v>-0.9316999999999991</v>
       </c>
       <c r="W26" t="n">
-        <v>2.8607</v>
+        <v>2.825</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.7926</v>
+        <v>-3.7567</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104510_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104510_W6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-2.8249</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104510_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-3.7567</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
